--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/3_Categorical Variables. Visualization techniques/Exercises/2.3.+Categorical+variables.+Visualization+techniques_exercise - completed.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/3_Categorical Variables. Visualization techniques/Exercises/2.3.+Categorical+variables.+Visualization+techniques_exercise - completed.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CB839D-DFD9-401A-A804-F09BCD323D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99D9454-07AB-4218-B7C5-7C4C2574EC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frequency distribution table" sheetId="4" r:id="rId1"/>
@@ -13,11 +13,19 @@
     <sheet name="Pie chart" sheetId="7" r:id="rId3"/>
     <sheet name="Pareto diagram" sheetId="12" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bar chart'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Frequency distribution table'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Pareto diagram'!$A$1:$H$40</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3695,16 +3703,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3731,16 +3739,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>118110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3772,16 +3780,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>731520</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4077,7 +4085,7 @@
   <cols>
     <col min="1" max="1" width="2" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="66.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="3"/>
   </cols>
@@ -4258,7 +4266,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4788,7 +4796,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5151,12 +5160,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:K22"/>
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5425,7 +5438,7 @@
     <sortCondition descending="1" ref="E13:E15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>